--- a/artfynd/A 17913-2019 artfynd.xlsx
+++ b/artfynd/A 17913-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17913-2019 artfynd.xlsx
+++ b/artfynd/A 17913-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86851042</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
+        <v>98092</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615689.084506036</v>
+        <v>615689</v>
       </c>
       <c r="R2" t="n">
-        <v>6862637.86594828</v>
+        <v>6862638</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +748,9 @@
           <t>2018-06-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 17913-2019 artfynd.xlsx
+++ b/artfynd/A 17913-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86851042</v>
       </c>
       <c r="B2" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 17913-2019 artfynd.xlsx
+++ b/artfynd/A 17913-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86851042</v>
       </c>
       <c r="B2" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 17913-2019 artfynd.xlsx
+++ b/artfynd/A 17913-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86851042</v>
       </c>
       <c r="B2" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 17913-2019 artfynd.xlsx
+++ b/artfynd/A 17913-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86851042</v>
       </c>
       <c r="B2" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>219790</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 17913-2019 artfynd.xlsx
+++ b/artfynd/A 17913-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86851042</v>
       </c>
       <c r="B2" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>219790</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 17913-2019 artfynd.xlsx
+++ b/artfynd/A 17913-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86851042</v>
       </c>
       <c r="B2" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 17913-2019 artfynd.xlsx
+++ b/artfynd/A 17913-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86851042</v>
       </c>
       <c r="B2" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 17913-2019 artfynd.xlsx
+++ b/artfynd/A 17913-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86851042</v>
       </c>
       <c r="B2" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 17913-2019 artfynd.xlsx
+++ b/artfynd/A 17913-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86851042</v>
       </c>
       <c r="B2" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 17913-2019 artfynd.xlsx
+++ b/artfynd/A 17913-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>86851042</v>
       </c>
       <c r="B2" t="n">
-        <v>98161</v>
+        <v>98264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
